--- a/Partial-Entries-Converted-to-Apps/06-29-26-google-partials-converted-to-apps-this-week.xlsx
+++ b/Partial-Entries-Converted-to-Apps/06-29-26-google-partials-converted-to-apps-this-week.xlsx
@@ -415,13 +415,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.9" customWidth="1" min="1" max="1"/>
-    <col width="15.4" customWidth="1" min="2" max="2"/>
-    <col width="18.7" customWidth="1" min="3" max="3"/>
-    <col width="38.5" customWidth="1" min="4" max="4"/>
+    <col width="19.8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="41.8" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -455,270 +455,459 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>003QP00001b34Si</t>
+          <t>003QP00001c6ecK</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Odie</t>
+          <t>nytoyia</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>laughlin</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>support@six-watch.org</t>
+          <t>nytoyialaughlin@gmail.com</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>06-15-2026</t>
+          <t>06-22-2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>003QP00001b5ob7</t>
+          <t>003QP00001c5oaX</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Halifa</t>
+          <t>Promise</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Rabiu Ibrahim</t>
+          <t>Adeniyi</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>rabiuhalifaibrahim@gmail.com</t>
+          <t>adeniyipromiseyanmife@gmail.com</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>06-15-2026</t>
+          <t>06-22-2026</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>003QP00001aWNW6</t>
+          <t>003QP00001cBfnq</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Kamala</t>
+          <t>MARIA</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Bhagat</t>
+          <t>ALMEIDA</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>bhagatk@vcu.edu</t>
+          <t>maria@partnertulsa.org</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>06-15-2026</t>
+          <t>06-23-2026</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>003QP00001b5lgZ</t>
+          <t>003QP00001W3p9a</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Salif</t>
+          <t>Eillee</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Guingani</t>
+          <t>Patuto</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>salifguingane@gmail.com</t>
+          <t>eillee.patuto@netech.edu</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>06-15-2026</t>
+          <t>06-23-2026</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>003QP00001b7dTR</t>
+          <t>003QP00001c7K6r</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Josephine</t>
+          <t>Muhammad Javed</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Agbakpe-Kafui</t>
+          <t>Kharuti</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>josephine.agbakpeka1@howard.edu</t>
+          <t>kharuti@gmail.com</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>06-15-2026</t>
+          <t>06-23-2026</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>003QP00001b8CKk</t>
+          <t>003QP00001aWNcF</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>مزاحم</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>مزاحم</t>
+          <t>Harrison</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>abu22551020@gmail.com</t>
+          <t>vharrison36@gmail.com</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>06-15-2026</t>
+          <t>06-23-2026</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bO8Jd</t>
+          <t>003QP00001cBfRg</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>George</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>Udunwa</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>kelechiwilliams17@gmail.com</t>
+          <t>info@tryfollowup.app</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>06-17-2026</t>
+          <t>06-23-2026</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bca4h</t>
+          <t>003QP00001cKbwN</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Obinna</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>Onyenahazi</t>
+          <t>Ortiz</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>onyenahazi@yahoo.com</t>
+          <t>info@tasteofoklahoma.com</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>06-18-2026</t>
+          <t>06-24-2026</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>003QP00001be0tB</t>
+          <t>003QP00001cJBz3</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>Danielle</t>
+          <t>Jasmine</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>Rich</t>
+          <t>Fluker</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>danielle@rich-results.com</t>
+          <t>jasmine@pivotalparadigmproject.org</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>06-18-2026</t>
+          <t>06-24-2026</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>003QP00001bxfRk</t>
+          <t>003QP00001cWtXd</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>Abdulganiy</t>
+          <t>Pradeep Kumar</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>Akorede</t>
+          <t>Kasi</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>akoredeabdulganiy1@gmail.com</t>
+          <t>kasipradeepkumar3@gmail.com</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>06-22-2026</t>
+          <t>06-25-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>003QP00001ckDSA</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Melvin</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Hall</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>melvin@interamec.org</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>06-26-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>003QP00001cgjn7</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Zac</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Doyle</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>doylez@pryorcreek.org</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>06-26-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>003QP00001cngCi</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>Norah</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Nafuna</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>nafunan8@gmail.com</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>06-27-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>003QP00001csrp0</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>Niki</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>Brunson Saunders</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>niki@alegacysolution.com</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>06-28-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>003QP00001cscbW</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>Madala</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>Mathurin</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>m@kavarihealth.com</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>06-28-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>003QP00001d081u</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Ayush</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Sharma</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>ayushsharma27127@gmail.com</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>06-29-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>003QP00001cxmRH</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>Ramadan</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>Abdul-Azeez</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>raazeez@bluemarbleinc.com</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>06-29-2026</t>
         </is>
       </c>
     </row>
